--- a/sports_forms/002_swimming_competition_enrollment--sports_forms.xlsx
+++ b/sports_forms/002_swimming_competition_enrollment--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>swimmer_event_time</t>
+          <t>swimmer_event_time_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>swimmer event time</t>
+          <t>Swimmer Event Time 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>swimmer_event_time</t>
+          <t>swimmer_event_time_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>swimmer event time</t>
+          <t>Swimmer Event Time 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>event_entrants</t>
+          <t>event_entrants_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>event entrants</t>
+          <t>Event Entrants 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>swimmer_event_time</t>
+          <t>swimmer_event_time_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>swimmer event time</t>
+          <t>Swimmer Event Time 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>swimmer_info</t>
+          <t>swimmer_info_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>swimmer info</t>
+          <t>Swimmer Info 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>swimmer_notes</t>
+          <t>swimmer_notes_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>swimmer notes</t>
+          <t>Swimmer Notes 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1409,63 +1409,63 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>event_entrants_choices</t>
+          <t>event_entrants_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>event_entrants_choices</t>
+          <t>event_entrants_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>event_entrants_choices</t>
+          <t>event_entrants_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
